--- a/Insurer_Master_Mapping.xlsx
+++ b/Insurer_Master_Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\OCR Policy Data\Test Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gireesh-Bizbma\Commission\Statements\Apr-2026\Sample of AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A75903C3-39F3-4E1E-B648-2AAECB5B3544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777CDE08-7C0C-485A-B33C-C4A509E0E04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8F1C480-8CB7-400E-AEDE-F804A810F386}"/>
   </bookViews>
@@ -232,9 +232,6 @@
     <t>Policy_Holder_Name</t>
   </si>
   <si>
-    <t>Commission</t>
-  </si>
-  <si>
     <t>TOTAL_AMT</t>
   </si>
   <si>
@@ -383,6 +380,9 @@
   </si>
   <si>
     <t>Premium_Before_GST</t>
+  </si>
+  <si>
+    <t>Premium</t>
   </si>
 </sst>
 </file>
@@ -925,10 +925,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1297,13 +1293,13 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1320,13 +1316,13 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1343,13 +1339,13 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1366,13 +1362,13 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1389,13 +1385,13 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1412,13 +1408,13 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1435,10 +1431,10 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1455,10 +1451,10 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1475,13 +1471,13 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1498,13 +1494,13 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1521,13 +1517,13 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1541,13 +1537,13 @@
         <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1561,10 +1557,10 @@
         <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1578,13 +1574,13 @@
         <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1598,13 +1594,13 @@
         <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1618,13 +1614,13 @@
         <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1638,13 +1634,13 @@
         <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1658,13 +1654,13 @@
         <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1678,13 +1674,13 @@
         <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1698,13 +1694,13 @@
         <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Insurer_Master_Mapping.xlsx
+++ b/Insurer_Master_Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gireesh-Bizbma\Commission\Statements\Apr-2026\Sample of AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777CDE08-7C0C-485A-B33C-C4A509E0E04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34751CB4-EE58-48C0-8DB0-EB64ECB334B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8F1C480-8CB7-400E-AEDE-F804A810F386}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="124">
   <si>
     <t>Insurer Company</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Product Name, Product</t>
   </si>
   <si>
-    <t>Product, Product Name</t>
-  </si>
-  <si>
     <t>CARE HEALTH INSURANCE LIMITED</t>
   </si>
   <si>
@@ -154,12 +151,6 @@
     <t>POLICY ID</t>
   </si>
   <si>
-    <t>D_Poll</t>
-  </si>
-  <si>
-    <t>Policy_No</t>
-  </si>
-  <si>
     <t>Policy/ Endt number</t>
   </si>
   <si>
@@ -208,12 +199,6 @@
     <t>CLIENT NAME</t>
   </si>
   <si>
-    <t>S Insuredname</t>
-  </si>
-  <si>
-    <t>Customer_name</t>
-  </si>
-  <si>
     <t>customer_Name</t>
   </si>
   <si>
@@ -256,12 +241,6 @@
     <t>TOTAL COMMISSION</t>
   </si>
   <si>
-    <t>TOTAL COMM</t>
-  </si>
-  <si>
-    <t>Total_commission</t>
-  </si>
-  <si>
     <t>final_grid_payable for invoicing</t>
   </si>
   <si>
@@ -274,9 +253,6 @@
     <t>Total Eligible</t>
   </si>
   <si>
-    <t>TOTAL_REWARD</t>
-  </si>
-  <si>
     <t>Total Expense</t>
   </si>
   <si>
@@ -301,12 +277,6 @@
     <t>POLICY ENTRY DATE</t>
   </si>
   <si>
-    <t>Policy Start Date</t>
-  </si>
-  <si>
-    <t>S Doi</t>
-  </si>
-  <si>
     <t>Policy_start_date</t>
   </si>
   <si>
@@ -325,9 +295,6 @@
     <t>Risk inc date</t>
   </si>
   <si>
-    <t>POLICY_INCEPTION_DATE</t>
-  </si>
-  <si>
     <t>Policy_Start_Date</t>
   </si>
   <si>
@@ -355,15 +322,6 @@
     <t>TOTAL PREMIUM REST ALL</t>
   </si>
   <si>
-    <t>Gross Written Premium</t>
-  </si>
-  <si>
-    <t>GROSS</t>
-  </si>
-  <si>
-    <t>Total_Premium</t>
-  </si>
-  <si>
     <t>ELG Premium Amount</t>
   </si>
   <si>
@@ -376,13 +334,64 @@
     <t>Net premium</t>
   </si>
   <si>
-    <t>TOTAL_PREMIUM</t>
-  </si>
-  <si>
     <t>Premium_Before_GST</t>
   </si>
   <si>
     <t>Premium</t>
+  </si>
+  <si>
+    <t>TOTAL_COMMISSION_AMOUNT</t>
+  </si>
+  <si>
+    <t>IRDA Product Name</t>
+  </si>
+  <si>
+    <t>GROSS_PREMIUM</t>
+  </si>
+  <si>
+    <t>Dpollno</t>
+  </si>
+  <si>
+    <t>Insuredname</t>
+  </si>
+  <si>
+    <t>CostingProduct</t>
+  </si>
+  <si>
+    <t>GrossAmt</t>
+  </si>
+  <si>
+    <t>TotalCommAmt</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Policy_No, Policy Number</t>
+  </si>
+  <si>
+    <t>Customer_name, Client Name</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Total_Premium, Total Premium</t>
+  </si>
+  <si>
+    <t>Total_commission, Commission</t>
+  </si>
+  <si>
+    <t>Policy Number</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Policy Inception Date</t>
   </si>
 </sst>
 </file>
@@ -1281,426 +1290,432 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
         <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
